--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
 If only a smaller degree of precision is usable
 (for example, only minute precision is meaningful),
 the following extension SHALL be used:
-http://314e.com/fhir/StructureDefinition/datetime-precision-314e</t>
+http://314e.com/fhir/StructureDefinition/datetime-precision</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -316,7 +316,7 @@
     <t>timePrecision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/datetime-precision-314e}
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/datetime-precision}
 </t>
   </si>
   <si>
@@ -660,7 +660,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-instant-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-instant-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
